--- a/GunfireDungeon_Godot/excel/AbnormalStateConfig@异常状态.xlsx
+++ b/GunfireDungeon_Godot/excel/AbnormalStateConfig@异常状态.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>Id</t>
   </si>
@@ -135,7 +135,8 @@
     <t>0.0714, 1</t>
   </si>
   <si>
-    <t>"AsContinuousDamage":[1,0.01,2]</t>
+    <t>"AsContinuousDamage":[1,0.01,2],
+"AsMoveSpeed":[0.2,true]</t>
   </si>
   <si>
     <t>每秒扣除（1%最大生命值+2）的生命值，移动速度+20%，持续15秒</t>
@@ -169,9 +170,6 @@
   </si>
   <si>
     <t>AsComp参数说明</t>
-  </si>
-  <si>
-    <t>附属参数</t>
   </si>
   <si>
     <t>AsContinuousDamage:每秒持续伤害，可以叠加多层
@@ -180,9 +178,9 @@
 参数3: 每秒失去生命值</t>
   </si>
   <si>
-    <t xml:space="preserve">LostPercentage:每秒失去生命值百分比,不填默认0
-LostValue:每秒失去生命值，不填默认0
-</t>
+    <t>AsMoveSpeed:移动速度加成，可以叠加多层
+参数1:移速增量
+参数2：增量是否是百分比,bool类型</t>
   </si>
 </sst>
 </file>
@@ -798,15 +796,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1182,190 +1177,190 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="19.6666666666667" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.65" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.0666666666667" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.0583333333333" style="3" customWidth="1"/>
-    <col min="5" max="7" width="20.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="40.975" style="3" customWidth="1"/>
-    <col min="9" max="9" width="58.6" style="3" customWidth="1"/>
-    <col min="10" max="10" width="44.0166666666667" style="3" customWidth="1"/>
-    <col min="11" max="11" width="43.3666666666667" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9" style="4"/>
+    <col min="1" max="1" width="19.6666666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.65" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.0666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.0583333333333" style="2" customWidth="1"/>
+    <col min="5" max="7" width="20.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="40.975" style="2" customWidth="1"/>
+    <col min="9" max="9" width="58.6" style="2" customWidth="1"/>
+    <col min="10" max="10" width="44.0166666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="43.3666666666667" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="31" customHeight="1" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="109" customHeight="1" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" ht="67" customHeight="1" spans="1:11">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" ht="65" customHeight="1" spans="1:11">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>3</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>6</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1379,28 +1374,89 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="B2:B25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="55.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="34.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="84" customHeight="1" spans="2:3">
+    <row r="2" ht="84" customHeight="1" spans="2:2">
       <c r="B2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" ht="123" customHeight="1" spans="2:2">
+      <c r="B3" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" ht="123" customHeight="1" spans="2:3">
-      <c r="B3" s="2" t="s">
+    <row r="4" ht="106" customHeight="1" spans="2:2">
+      <c r="B4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>46</v>
-      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GunfireDungeon_Godot/excel/AbnormalStateConfig@异常状态.xlsx
+++ b/GunfireDungeon_Godot/excel/AbnormalStateConfig@异常状态.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -167,6 +167,24 @@
   </si>
   <si>
     <t>res://resource/sprite/tip/PoisonMask.png</t>
+  </si>
+  <si>
+    <t>出血</t>
+  </si>
+  <si>
+    <t>0, 0</t>
+  </si>
+  <si>
+    <t>"AsDamage":[0.15,10]</t>
+  </si>
+  <si>
+    <t>受到15%最大生命值+10的伤害</t>
+  </si>
+  <si>
+    <t>res://resource/sprite/tip/Bleeding.png</t>
+  </si>
+  <si>
+    <t>res://resource/sprite/tip/BleedingMask.png</t>
   </si>
   <si>
     <t>AsComp参数说明</t>
@@ -181,6 +199,11 @@
     <t>AsMoveSpeed:移动速度加成，可以叠加多层
 参数1:移速增量
 参数2：增量是否是百分比,bool类型</t>
+  </si>
+  <si>
+    <t>AsDamage:单次伤害,不可叠加，触发后立即移除该异常状态，造成的伤害计算方式为(参数1+参数2)
+参数1：最大生命值百分比
+参数2：具体伤害值</t>
   </si>
 </sst>
 </file>
@@ -1174,8 +1197,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="19.6666666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.65" style="2" customWidth="1"/>
@@ -1362,6 +1385,41 @@
       </c>
       <c r="K5" s="2" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="6" ht="41" customHeight="1" spans="1:11">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1382,21 +1440,23 @@
   <sheetData>
     <row r="2" ht="84" customHeight="1" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="123" customHeight="1" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="106" customHeight="1" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="2"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1" spans="2:2">
+      <c r="B5" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="2"/>

--- a/GunfireDungeon_Godot/excel/AbnormalStateConfig@异常状态.xlsx
+++ b/GunfireDungeon_Godot/excel/AbnormalStateConfig@异常状态.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24765" windowHeight="12495"/>
+    <workbookView windowHeight="19180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -64,7 +64,7 @@
     <t>IconMask</t>
   </si>
   <si>
-    <t>异常状态类型id，和AbnormalStateType枚举索引对应</t>
+    <t>异常状态类型id，和AbnormalStateType枚举名称对应</t>
   </si>
   <si>
     <t>名称</t>
@@ -117,10 +117,52 @@
     <t>{string:[object]}*</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>燃烧</t>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>1, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6, 1.7, 1.8, 1.9</t>
+  </si>
+  <si>
+    <t>0.142857, 1</t>
+  </si>
+  <si>
+    <t>"AsContinuousDamage":[1,0.005,1]</t>
+  </si>
+  <si>
+    <t>累计中毒可以叠加层数，每层每秒受到（0.5%最大生命值+1）的生命值，每层持续8秒</t>
+  </si>
+  <si>
+    <t>res://resource/sprite/tip/Poison.png</t>
+  </si>
+  <si>
+    <t>res://resource/sprite/tip/PoisonMask.png</t>
+  </si>
+  <si>
+    <t>Bleeding</t>
+  </si>
+  <si>
+    <t>出血</t>
+  </si>
+  <si>
+    <t>0, 0</t>
+  </si>
+  <si>
+    <t>"AsDamage":[0.15,10]</t>
+  </si>
+  <si>
+    <t>受到15%最大生命值+10的伤害</t>
+  </si>
+  <si>
+    <t>res://resource/sprite/tip/Bleeding.png</t>
+  </si>
+  <si>
+    <t>res://resource/sprite/tip/BleedingMask.png</t>
+  </si>
+  <si>
+    <t>Ignite</t>
+  </si>
+  <si>
+    <t>点燃</t>
   </si>
   <si>
     <t>1</t>
@@ -148,43 +190,52 @@
     <t>res://resource/sprite/tip/FireMask.png</t>
   </si>
   <si>
-    <t>中毒</t>
-  </si>
-  <si>
-    <t>1, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6, 1.7, 1.8, 1.9</t>
-  </si>
-  <si>
-    <t>0.142857, 1</t>
-  </si>
-  <si>
-    <t>"AsContinuousDamage":[1,0.005,1]</t>
-  </si>
-  <si>
-    <t>累计中毒可以叠加层数，每层每秒受到（0.5%最大生命值+1）的生命值，每层持续8秒</t>
-  </si>
-  <si>
-    <t>res://resource/sprite/tip/Poison.png</t>
-  </si>
-  <si>
-    <t>res://resource/sprite/tip/PoisonMask.png</t>
-  </si>
-  <si>
-    <t>出血</t>
-  </si>
-  <si>
-    <t>0, 0</t>
-  </si>
-  <si>
-    <t>"AsDamage":[0.15,10]</t>
-  </si>
-  <si>
-    <t>受到15%最大生命值+10的伤害</t>
-  </si>
-  <si>
-    <t>res://resource/sprite/tip/Bleeding.png</t>
-  </si>
-  <si>
-    <t>res://resource/sprite/tip/BleedingMask.png</t>
+    <t>ShortCircuit</t>
+  </si>
+  <si>
+    <t>短路</t>
+  </si>
+  <si>
+    <t>Interference</t>
+  </si>
+  <si>
+    <t>干扰</t>
+  </si>
+  <si>
+    <t>ElectricShock</t>
+  </si>
+  <si>
+    <t>触电</t>
+  </si>
+  <si>
+    <t>Corrosion</t>
+  </si>
+  <si>
+    <t>腐蚀</t>
+  </si>
+  <si>
+    <t>Fragile</t>
+  </si>
+  <si>
+    <t>脆弱</t>
+  </si>
+  <si>
+    <t>Blind</t>
+  </si>
+  <si>
+    <t>致盲</t>
+  </si>
+  <si>
+    <t>Chaos</t>
+  </si>
+  <si>
+    <t>混沌</t>
+  </si>
+  <si>
+    <t>ArmorBreak</t>
+  </si>
+  <si>
+    <t>破甲</t>
   </si>
   <si>
     <t>AsComp参数说明</t>
@@ -1197,18 +1248,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="19.6666666666667" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.65" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27.0666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.0583333333333" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.6634615384615" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.6538461538462" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.0673076923077" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.0576923076923" style="2" customWidth="1"/>
     <col min="5" max="7" width="20.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="40.975" style="2" customWidth="1"/>
-    <col min="9" max="9" width="58.6" style="2" customWidth="1"/>
-    <col min="10" max="10" width="44.0166666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="43.3666666666667" style="3" customWidth="1"/>
+    <col min="8" max="8" width="40.9711538461538" style="2" customWidth="1"/>
+    <col min="9" max="9" width="58.5961538461538" style="2" customWidth="1"/>
+    <col min="10" max="10" width="44.0192307692308" style="2" customWidth="1"/>
+    <col min="11" max="11" width="43.3653846153846" style="3" customWidth="1"/>
     <col min="12" max="12" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -1317,109 +1368,170 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="67" customHeight="1" spans="1:11">
-      <c r="A4" s="4" t="s">
+    <row r="4" ht="65" customHeight="1" spans="2:11">
+      <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="I4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="J4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="K4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="2" t="s">
+    </row>
+    <row r="5" ht="41" customHeight="1" spans="1:11">
+      <c r="A5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="65" customHeight="1" spans="1:11">
-      <c r="A5" s="2">
+      <c r="C5" s="2">
         <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="2" t="s">
+    </row>
+    <row r="6" ht="67" customHeight="1" spans="1:11">
+      <c r="A6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" ht="41" customHeight="1" spans="1:11">
-      <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <v>7</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="F6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="H6" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" ht="17" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" ht="17" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" ht="17" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" ht="17" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" ht="17" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1433,29 +1545,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B2:B25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="55.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="84" customHeight="1" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" ht="123" customHeight="1" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="106" customHeight="1" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" ht="70" customHeight="1" spans="2:2">
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:2">
@@ -1529,7 +1641,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
